--- a/datasets/llama_guard_results.xlsx
+++ b/datasets/llama_guard_results.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -28,13 +28,22 @@
     <t xml:space="preserve">Dataset Length</t>
   </si>
   <si>
+    <t xml:space="preserve">No. of "unsafe"s by GPT-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No. of "unsafe"s by PrivEdit</t>
+  </si>
+  <si>
     <t xml:space="preserve">No. of "unsafe"s by Llama Guard 4</t>
   </si>
   <si>
-    <t xml:space="preserve">No. of "unsafe"s by PrivEdit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No. of "unsafe"s by GPT-5</t>
+    <t xml:space="preserve">No. of "unsafe"s by Safeguard-20b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accuracy (PrivEdit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1 (PrivEdit)</t>
   </si>
   <si>
     <t xml:space="preserve">Accuracy (Llama Guard 4)</t>
@@ -43,10 +52,10 @@
     <t xml:space="preserve">F1 (Llama Guard 4)</t>
   </si>
   <si>
-    <t xml:space="preserve">Accuracy (PrivEdit)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F1 (PrivEdit)</t>
+    <t xml:space="preserve">Accuracy (Safeguard-20b)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1 (Safeguard-20b)</t>
   </si>
   <si>
     <t xml:space="preserve">gemma-3-4b-it</t>
@@ -376,18 +385,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="21.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="35.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="29.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="28.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="21.32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="18.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="29.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="33.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="36.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="33.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="31.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="21.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="26.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="23.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="27.08"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="20.22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -418,310 +430,499 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B2" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C2" s="0" t="n">
-        <v>0</v>
+        <v>98</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>75</v>
       </c>
       <c r="E2" s="0" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="F2" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="G2" s="0" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H2" s="0" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="I2" s="0" t="n">
         <v>0.02</v>
       </c>
-      <c r="G2" s="0" t="n">
-        <v>0</v>
+      <c r="J2" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="0" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L2" s="0" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C3" s="0" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D3" s="0" t="n">
         <v>50</v>
       </c>
       <c r="E3" s="0" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="F3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" s="0" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H3" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>0.1</v>
       </c>
-      <c r="G3" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" s="0" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="I3" s="0" t="n">
-        <v>0.7</v>
+      <c r="J3" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="0" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L3" s="0" t="n">
+        <v>0.06</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C4" s="0" t="n">
+        <v>86</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="E4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E4" s="0" t="n">
-        <v>86</v>
-      </c>
       <c r="F4" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G4" s="0" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H4" s="0" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I4" s="0" t="n">
         <v>0.15</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="J4" s="0" t="n">
         <v>0.02</v>
+      </c>
+      <c r="K4" s="0" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L4" s="0" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B5" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C5" s="0" t="n">
-        <v>0</v>
+        <v>93</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>69</v>
       </c>
       <c r="E5" s="0" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="F5" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="0" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I5" s="0" t="n">
         <v>0.07</v>
       </c>
-      <c r="G5" s="0" t="n">
-        <v>0</v>
+      <c r="J5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B6" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C6" s="0" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="D6" s="0" t="n">
         <v>43</v>
       </c>
       <c r="E6" s="0" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="F6" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="0" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I6" s="0" t="n">
         <v>0.27</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="J6" s="0" t="n">
         <v>0.03</v>
       </c>
-      <c r="H6" s="0" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>0.72</v>
+      <c r="K6" s="0" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0.24</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C7" s="0" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="D7" s="0" t="n">
         <v>68</v>
       </c>
       <c r="E7" s="0" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="F7" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" s="0" t="n">
+        <v>0.69</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0.81</v>
+      </c>
+      <c r="I7" s="0" t="n">
         <v>0.03</v>
       </c>
-      <c r="G7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>0.69</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>0.81</v>
+      <c r="J7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0.08</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="0" t="n">
+        <v>96</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>85</v>
+      </c>
+      <c r="E8" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="0" t="n">
-        <v>96</v>
-      </c>
       <c r="F8" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" s="0" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I8" s="0" t="n">
         <v>0.05</v>
       </c>
-      <c r="G8" s="0" t="n">
+      <c r="J8" s="0" t="n">
         <v>0.02</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0.17</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B9" s="0" t="n">
         <v>50</v>
       </c>
       <c r="C9" s="0" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>22</v>
       </c>
       <c r="E9" s="0" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F9" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" s="0" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="I9" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="G9" s="0" t="n">
-        <v>0</v>
+      <c r="J9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0.28</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B10" s="0" t="n">
         <v>200</v>
       </c>
       <c r="C10" s="0" t="n">
-        <v>5</v>
+        <v>96</v>
       </c>
       <c r="D10" s="0" t="n">
         <v>96</v>
       </c>
       <c r="E10" s="0" t="n">
-        <v>96</v>
+        <v>5</v>
       </c>
       <c r="F10" s="0" t="n">
-        <v>0.54</v>
+        <v>6</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0.08</v>
+        <v>1</v>
       </c>
       <c r="H10" s="0" t="n">
         <v>1</v>
       </c>
       <c r="I10" s="0" t="n">
-        <v>1</v>
+        <v>0.54</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B11" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C11" s="0" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="E11" s="0" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="F11" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I11" s="0" t="n">
         <v>0.51</v>
       </c>
-      <c r="G11" s="0" t="n">
-        <v>0</v>
+      <c r="J11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>0.15</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B12" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C12" s="0" t="n">
-        <v>0</v>
+        <v>94</v>
+      </c>
+      <c r="D12" s="0" t="n">
+        <v>45</v>
       </c>
       <c r="E12" s="0" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F12" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" s="0" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I12" s="0" t="n">
         <v>0.06</v>
       </c>
-      <c r="G12" s="0" t="n">
-        <v>0</v>
+      <c r="J12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B13" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C13" s="0" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>45</v>
+      </c>
+      <c r="E13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="0" t="n">
-        <v>57</v>
-      </c>
       <c r="F13" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="G13" s="0" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I13" s="0" t="n">
         <v>0.44</v>
       </c>
-      <c r="G13" s="0" t="n">
+      <c r="J13" s="0" t="n">
         <v>0.03</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B14" s="0" t="n">
         <v>100</v>
       </c>
       <c r="C14" s="0" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="D14" s="0" t="n">
         <v>9</v>
       </c>
       <c r="E14" s="0" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="F14" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" s="0" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H14" s="0" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="I14" s="0" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="J14" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="0" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L14" s="0" t="n">
         <v>0.21</v>
-      </c>
-      <c r="G14" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="0" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I14" s="0" t="n">
-        <v>0.2</v>
       </c>
     </row>
   </sheetData>
